--- a/01_analyses_states/Uttarakhand/results/SoIB_summaries.xlsx
+++ b/01_analyses_states/Uttarakhand/results/SoIB_summaries.xlsx
@@ -396,13 +396,10 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>2</v>
-      </c>
-      <c r="D2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>33.3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">
@@ -417,9 +414,6 @@
       <c r="C3">
         <v>0</v>
       </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
       <c r="E3">
         <v>0</v>
       </c>
@@ -431,16 +425,13 @@
         </is>
       </c>
       <c r="B4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4">
         <v>4</v>
       </c>
-      <c r="D4">
-        <v>100</v>
-      </c>
       <c r="E4">
-        <v>66.7</v>
+        <v>80</v>
       </c>
     </row>
     <row r="5">
@@ -455,9 +446,6 @@
       <c r="C5">
         <v>0</v>
       </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
       <c r="E5">
         <v>0</v>
       </c>
@@ -474,9 +462,6 @@
       <c r="C6">
         <v>0</v>
       </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
       <c r="E6">
         <v>0</v>
       </c>
@@ -488,10 +473,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="C7">
-        <v>78</v>
+        <v>86</v>
       </c>
     </row>
     <row r="8">
@@ -501,10 +486,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>540</v>
+        <v>535</v>
       </c>
       <c r="C8">
-        <v>520</v>
+        <v>512</v>
       </c>
     </row>
   </sheetData>
@@ -643,7 +628,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
   </sheetData>
@@ -680,7 +665,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="3">
@@ -690,10 +675,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -703,10 +688,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="C4">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">

--- a/01_analyses_states/Uttarakhand/results/SoIB_summaries.xlsx
+++ b/01_analyses_states/Uttarakhand/results/SoIB_summaries.xlsx
@@ -398,11 +398,8 @@
       <c r="C2">
         <v>1</v>
       </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
       <c r="E2">
-        <v>16.7</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">
@@ -417,9 +414,6 @@
       <c r="C3">
         <v>0</v>
       </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
       <c r="E3">
         <v>0</v>
       </c>
@@ -431,16 +425,13 @@
         </is>
       </c>
       <c r="B4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4">
-        <v>5</v>
-      </c>
-      <c r="D4">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="E4">
-        <v>83.3</v>
+        <v>80</v>
       </c>
     </row>
     <row r="5">
@@ -455,9 +446,6 @@
       <c r="C5">
         <v>0</v>
       </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
       <c r="E5">
         <v>0</v>
       </c>
@@ -474,9 +462,6 @@
       <c r="C6">
         <v>0</v>
       </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
       <c r="E6">
         <v>0</v>
       </c>
@@ -488,10 +473,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="C7">
-        <v>78</v>
+        <v>86</v>
       </c>
     </row>
     <row r="8">
@@ -501,10 +486,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>540</v>
+        <v>535</v>
       </c>
       <c r="C8">
-        <v>520</v>
+        <v>512</v>
       </c>
     </row>
   </sheetData>
@@ -643,7 +628,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
   </sheetData>
@@ -680,7 +665,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="3">
@@ -690,10 +675,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -703,10 +688,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="C4">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">

--- a/01_analyses_states/Uttarakhand/results/SoIB_summaries.xlsx
+++ b/01_analyses_states/Uttarakhand/results/SoIB_summaries.xlsx
@@ -393,13 +393,16 @@
         </is>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
+      <c r="D2">
+        <v>28.6</v>
+      </c>
       <c r="E2">
-        <v>20</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="3">
@@ -409,13 +412,16 @@
         </is>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="D3">
+        <v>14.3</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4">
@@ -425,13 +431,16 @@
         </is>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C4">
-        <v>4</v>
+        <v>19</v>
+      </c>
+      <c r="D4">
+        <v>42.9</v>
       </c>
       <c r="E4">
-        <v>80</v>
+        <v>82.59999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -441,10 +450,13 @@
         </is>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C5">
         <v>0</v>
+      </c>
+      <c r="D5">
+        <v>14.3</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -462,6 +474,9 @@
       <c r="C6">
         <v>0</v>
       </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
       <c r="E6">
         <v>0</v>
       </c>
@@ -473,10 +488,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C7">
-        <v>86</v>
+        <v>72</v>
       </c>
     </row>
     <row r="8">
@@ -486,10 +501,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>535</v>
+        <v>523</v>
       </c>
       <c r="C8">
-        <v>512</v>
+        <v>500</v>
       </c>
     </row>
   </sheetData>
@@ -618,7 +633,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>286</v>
+        <v>387</v>
       </c>
     </row>
     <row r="4">
@@ -628,7 +643,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>553</v>
+        <v>441</v>
       </c>
     </row>
   </sheetData>
@@ -665,7 +680,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>603</v>
+        <v>595</v>
       </c>
     </row>
     <row r="3">
@@ -675,10 +690,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
@@ -688,10 +703,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C4">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5">
@@ -748,16 +763,16 @@
         </is>
       </c>
       <c r="B2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C2">
-        <v>61.2</v>
+        <v>62.1</v>
       </c>
       <c r="D2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E2">
-        <v>75</v>
+        <v>72.7</v>
       </c>
     </row>
     <row r="3">
@@ -767,16 +782,16 @@
         </is>
       </c>
       <c r="B3">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C3">
-        <v>38.8</v>
+        <v>37.9</v>
       </c>
       <c r="D3">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E3">
-        <v>25</v>
+        <v>27.3</v>
       </c>
     </row>
   </sheetData>
